--- a/tests/fixtures/sample_chart.xlsx
+++ b/tests/fixtures/sample_chart.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="GuidePin" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="BushPin" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="GuideBush" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ReturnPin" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Bolts" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Plates" sheetId="5" state="visible" r:id="rId5"/>

--- a/tests/fixtures/sample_chart.xlsx
+++ b/tests/fixtures/sample_chart.xlsx
@@ -11,7 +11,11 @@
     <sheet name="GuideBush" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ReturnPin" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Bolts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Plates" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DowellingSleeve" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="HookStrip" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="EjectorGuidePin" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="EjectorGuideBush" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="LocatingRing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,27 +432,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>MainDiameter</t>
+          <t>Diameter C</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>OtherDiameter</t>
+          <t>Diameter F</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>TotalLength</t>
+          <t>Diameter G</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Total Cost</t>
         </is>
       </c>
     </row>
@@ -462,13 +466,13 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
         <v>50</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.5</v>
       </c>
       <c r="F2" t="n">
         <v>120</v>
@@ -484,13 +488,13 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
         <v>100</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.8</v>
       </c>
       <c r="F3" t="n">
         <v>160</v>
@@ -506,13 +510,13 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
         <v>50</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.6</v>
       </c>
       <c r="F4" t="n">
         <v>140</v>
@@ -528,13 +532,13 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
         <v>100</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
@@ -562,27 +566,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Diameter</t>
+          <t>Diameter C</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>OtherDiameter</t>
+          <t>Diameter D</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>TotalLength</t>
+          <t>Diameter E</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Total Cost</t>
         </is>
       </c>
     </row>
@@ -596,13 +600,13 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
         <v>50</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.4</v>
       </c>
       <c r="F2" t="n">
         <v>90</v>
@@ -618,13 +622,13 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
         <v>100</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.6</v>
       </c>
       <c r="F3" t="n">
         <v>130</v>
@@ -640,13 +644,13 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
         <v>50</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.5</v>
       </c>
       <c r="F4" t="n">
         <v>110</v>
@@ -663,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,10 +678,20 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Length</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
@@ -688,9 +702,15 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
         <v>50</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>60</v>
       </c>
     </row>
@@ -699,9 +719,15 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
         <v>63</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>75</v>
       </c>
     </row>
@@ -710,9 +736,15 @@
         <v>16</v>
       </c>
       <c r="B4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
         <v>100</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>110</v>
       </c>
     </row>
@@ -748,8 +780,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>6</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>20</v>
@@ -759,8 +793,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>8</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
       </c>
       <c r="B3" t="n">
         <v>25</v>
@@ -770,8 +806,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>10</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
       </c>
       <c r="B4" t="n">
         <v>30</v>
@@ -797,12 +835,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Density</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -812,29 +850,237 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Mild Steel</t>
-        </is>
+      <c r="A2" t="n">
+        <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>7.849999999999999e-06</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
+      <c r="A3" t="n">
+        <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>2.7e-06</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>250</v>
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D3" t="n">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3" t="n">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3" t="n">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" t="n">
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/sample_chart.xlsx
+++ b/tests/fixtures/sample_chart.xlsx
@@ -16,6 +16,7 @@
     <sheet name="EjectorGuidePin" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="EjectorGuideBush" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="LocatingRing" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="PlateThickness" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,6 +550,82 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/tests/fixtures/sample_chart.xlsx
+++ b/tests/fixtures/sample_chart.xlsx
@@ -17,6 +17,7 @@
     <sheet name="EjectorGuideBush" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="LocatingRing" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="PlateThickness" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Cavityhousingdrilling" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -626,6 +627,127 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Thickness</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24-30</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>38-48</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>24-30</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>38-48</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>24-30</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>38-48</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>195</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/tests/fixtures/sample_chart.xlsx
+++ b/tests/fixtures/sample_chart.xlsx
@@ -18,6 +18,8 @@
     <sheet name="LocatingRing" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="PlateThickness" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Cavityhousingdrilling" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SpacerBlocksCosting" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="BoltStandards" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -748,6 +750,166 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Thickness</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>24-30</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30-48</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>48-60</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>60-80</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>80-100</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>630</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Bolt Dia</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Clearance hole dia</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Counter bore dia</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Counter bore depth</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1034,7 +1196,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Outer dia</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">

--- a/tests/fixtures/sample_chart.xlsx
+++ b/tests/fixtures/sample_chart.xlsx
@@ -19,7 +19,9 @@
     <sheet name="PlateThickness" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Cavityhousingdrilling" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="SpacerBlocksCosting" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="BoltStandards" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="PunchHousingDrilling" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="PunchBackPlate" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="BoltStandards" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -832,6 +834,338 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Thickness</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24-30</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>38-48</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>48-60</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>24-30</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>38-48</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>48-60</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24-30</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>38-48</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>48-60</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1090</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Thickness</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24-30</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>38-48</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>48-60</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>24-30</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>38-48</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>48-60</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24-30</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>38-48</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>48-60</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
